--- a/artfynd/A 10440-2024 artfynd.xlsx
+++ b/artfynd/A 10440-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,65 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116399365</v>
+        <v>124114024</v>
       </c>
       <c r="B2" t="n">
-        <v>57283</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tomtmyr, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>709393</v>
+        <v>709263</v>
       </c>
       <c r="R2" t="n">
-        <v>6395387</v>
+        <v>6395367</v>
       </c>
       <c r="S2" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,12 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>NVI för ny elledning mellan Slite och visby</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,27 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119645847</v>
+        <v>116399365</v>
       </c>
       <c r="B3" t="n">
-        <v>57316</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,28 +805,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Tomtmyr, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>709411</v>
+        <v>709393</v>
       </c>
       <c r="R3" t="n">
         <v>6395387</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -896,6 +883,315 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>119645847</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57966</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>709411</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6395387</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124114022</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>709397</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6395353</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>NVI för ny elledning mellan Slite och visby</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>124114023</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>709257</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6395357</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Fole</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>NVI för ny elledning mellan Slite och visby</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10440-2024 artfynd.xlsx
+++ b/artfynd/A 10440-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124114024</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116399365</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119645847</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124114022</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,8 +1217,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124114023</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>